--- a/administrative_forms/049_store_employee_termination_offboarding_form--administrative_forms.xlsx
+++ b/administrative_forms/049_store_employee_termination_offboarding_form--administrative_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>separation_allowances</t>
+          <t>separation_allowances_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Separation Allowances</t>
+          <t>Separation Allowances 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>notice_period</t>
+          <t>notice_period_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Notice Period</t>
+          <t>Notice Period 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>termination_date</t>
+          <t>termination_date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Termination Date</t>
+          <t>Termination Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>termination_reason</t>
+          <t>termination_reason_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Termination Reason</t>
+          <t>Termination Reason 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>last_day_worked</t>
+          <t>last_day_worked_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Last Day Worked</t>
+          <t>Last Day Worked 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>separation_package</t>
+          <t>separation_package_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Separation Package</t>
+          <t>Separation Package 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
